--- a/inst/ext_data/French_FADN_desc_stats.xlsx
+++ b/inst/ext_data/French_FADN_desc_stats.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="7"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="rica20_cat" sheetId="1" state="visible" r:id="rId3"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1696" uniqueCount="915">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1697" uniqueCount="916">
   <si>
     <t xml:space="preserve">Variable</t>
   </si>
@@ -823,6 +823,9 @@
   </si>
   <si>
     <t xml:space="preserve">VLLAC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXTR2</t>
   </si>
   <si>
     <t xml:space="preserve">CODE3</t>
@@ -2858,7 +2861,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2881,10 +2884,6 @@
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -5671,7 +5670,30 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1"/>
+      <c r="A20" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="B20" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="C20" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="D20" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="F20" s="0" t="n">
+        <v>50</v>
+      </c>
+      <c r="G20" s="0" t="n">
+        <v>75</v>
+      </c>
+      <c r="H20" s="0" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -5715,1425 +5737,1425 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>159</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>48</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>145</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>123</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>21</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>21</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>29</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B41" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="D41" s="2" t="s">
         <v>358</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="C51" s="6"/>
-      <c r="D51" s="6"/>
+        <v>384</v>
+      </c>
+      <c r="C51" s="4"/>
+      <c r="D51" s="4"/>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>156</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>97</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>108</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>68</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>159</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>32</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>174</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>425</v>
-      </c>
-      <c r="C73" s="6"/>
-      <c r="D73" s="6"/>
+        <v>426</v>
+      </c>
+      <c r="C73" s="4"/>
+      <c r="D73" s="4"/>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>73</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B76" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="D76" s="2" t="s">
         <v>430</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="D76" s="2" t="s">
-        <v>429</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="C79" s="6"/>
-      <c r="D79" s="6"/>
+        <v>281</v>
+      </c>
+      <c r="C79" s="4"/>
+      <c r="D79" s="4"/>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>29</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>78</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>62</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>88</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>445</v>
-      </c>
-      <c r="C87" s="6"/>
-      <c r="D87" s="6"/>
+        <v>446</v>
+      </c>
+      <c r="C87" s="4"/>
+      <c r="D87" s="4"/>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>29</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>469</v>
-      </c>
-      <c r="C98" s="6"/>
-      <c r="D98" s="6"/>
+        <v>470</v>
+      </c>
+      <c r="C98" s="4"/>
+      <c r="D98" s="4"/>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>470</v>
-      </c>
-      <c r="C99" s="6"/>
-      <c r="D99" s="6"/>
+        <v>471</v>
+      </c>
+      <c r="C99" s="4"/>
+      <c r="D99" s="4"/>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>32</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>62</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>129</v>
@@ -7142,110 +7164,110 @@
         <v>23</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>38</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>8</v>
@@ -7254,64 +7276,64 @@
         <v>98</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>43</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C117" s="6"/>
-      <c r="D117" s="6"/>
+      <c r="C117" s="4"/>
+      <c r="D117" s="4"/>
     </row>
     <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>26</v>
@@ -7320,35 +7342,35 @@
         <v>174</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>29</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>32</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
   </sheetData>
@@ -7398,13 +7420,13 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>225</v>
@@ -7419,12 +7441,12 @@
         <v>225</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>225</v>
@@ -7450,13 +7472,13 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>225</v>
@@ -7471,18 +7493,18 @@
         <v>225</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>225</v>
@@ -7497,18 +7519,18 @@
         <v>225</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>225</v>
@@ -7523,18 +7545,18 @@
         <v>225</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>225</v>
@@ -7549,18 +7571,18 @@
         <v>225</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>225</v>
@@ -7572,21 +7594,21 @@
         <v>225</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>225</v>
@@ -7598,21 +7620,21 @@
         <v>225</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>225</v>
@@ -7624,21 +7646,21 @@
         <v>225</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>225</v>
@@ -7650,33 +7672,33 @@
         <v>225</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>225</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>249</v>
@@ -7684,13 +7706,13 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>225</v>
@@ -7705,18 +7727,18 @@
         <v>225</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>225</v>
@@ -7731,18 +7753,18 @@
         <v>225</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>225</v>
@@ -7757,18 +7779,18 @@
         <v>225</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>225</v>
@@ -7783,18 +7805,18 @@
         <v>225</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>225</v>
@@ -7809,18 +7831,18 @@
         <v>225</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>225</v>
@@ -7832,21 +7854,21 @@
         <v>225</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>225</v>
@@ -7858,21 +7880,21 @@
         <v>225</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>225</v>
@@ -7884,21 +7906,21 @@
         <v>225</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>225</v>
@@ -7918,16 +7940,16 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>225</v>
@@ -7936,41 +7958,41 @@
         <v>225</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>225</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>225</v>
@@ -8029,718 +8051,718 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>145</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>65</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>172</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>647</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>645</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>646</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>644</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>80</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>29</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>686</v>
-      </c>
-      <c r="C39" s="6"/>
-      <c r="D39" s="6"/>
+        <v>687</v>
+      </c>
+      <c r="C39" s="4"/>
+      <c r="D39" s="4"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>687</v>
-      </c>
-      <c r="C40" s="6"/>
-      <c r="D40" s="6"/>
+        <v>688</v>
+      </c>
+      <c r="C40" s="4"/>
+      <c r="D40" s="4"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>72</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>700</v>
-      </c>
-      <c r="C49" s="6"/>
-      <c r="D49" s="6"/>
+        <v>701</v>
+      </c>
+      <c r="C49" s="4"/>
+      <c r="D49" s="4"/>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>29</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>32</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
     </row>
   </sheetData>
@@ -8790,39 +8812,39 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>225</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>225</v>
@@ -8837,18 +8859,18 @@
         <v>225</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>225</v>
@@ -8863,70 +8885,70 @@
         <v>225</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>225</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>225</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>225</v>
@@ -8935,24 +8957,24 @@
         <v>225</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>225</v>
@@ -8967,18 +8989,18 @@
         <v>225</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>225</v>
@@ -8993,70 +9015,70 @@
         <v>225</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>225</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>225</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>225</v>
@@ -9065,65 +9087,65 @@
         <v>225</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>225</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
     </row>
   </sheetData>
@@ -9161,376 +9183,376 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>80</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>791</v>
-      </c>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
+        <v>792</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>62</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>29</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>88</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>29</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>32</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
   </sheetData>
@@ -9580,13 +9602,13 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>225</v>
@@ -9598,15 +9620,15 @@
         <v>225</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>225</v>
@@ -9632,13 +9654,13 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>225</v>
@@ -9653,12 +9675,12 @@
         <v>225</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>225</v>
@@ -9684,7 +9706,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>225</v>
@@ -9710,39 +9732,39 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>225</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>225</v>
@@ -9757,18 +9779,18 @@
         <v>225</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>225</v>
@@ -9788,13 +9810,13 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>225</v>
@@ -9803,24 +9825,24 @@
         <v>225</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>225</v>
@@ -9832,21 +9854,21 @@
         <v>225</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>225</v>
@@ -9861,12 +9883,12 @@
         <v>225</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>225</v>
@@ -9892,13 +9914,13 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>225</v>
@@ -9913,18 +9935,18 @@
         <v>225</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>225</v>
@@ -9939,18 +9961,18 @@
         <v>225</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>225</v>
@@ -9965,90 +9987,90 @@
         <v>225</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>225</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>225</v>
